--- a/output/laminas_comunales/comunal_p_aps_a_2020_magallanes.xlsx
+++ b/output/laminas_comunales/comunal_p_aps_a_2020_magallanes.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,97 +384,2197 @@
         </is>
       </c>
       <c r="C2">
-        <v>48.71794891357422</v>
+        <v>136649.828125</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>12301</t>
+          <t>12201</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Porvenir</t>
+          <t>Cabo de Hornos</t>
         </is>
       </c>
       <c r="C3">
-        <v>45.72930526733398</v>
+        <v>133624.3125</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>12401</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Natales</t>
+          <t>Río Verde</t>
         </is>
       </c>
       <c r="C4">
-        <v>44.74260711669922</v>
+        <v>133476.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12102</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Laguna Blanca</t>
+          <t>Río Verde</t>
         </is>
       </c>
       <c r="C5">
-        <v>44.44444274902344</v>
+        <v>132522.546875</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>12201</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Punta Arenas</t>
+          <t>Cabo de Hornos</t>
         </is>
       </c>
       <c r="C6">
-        <v>41.85519027709961</v>
+        <v>129598.0625</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>12103</t>
+          <t>12102</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Río Verde</t>
+          <t>Laguna Blanca</t>
         </is>
       </c>
       <c r="C7">
-        <v>37.03703689575195</v>
+        <v>129367.1796875</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>128114.1640625</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>127531.0859375</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>126560.734375</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>125970.375</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>125905.0078125</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>125310.546875</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>124305.5390625</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>123658.328125</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>122458.0078125</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>121927.71875</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>12302</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Primavera</t>
         </is>
       </c>
-      <c r="C8">
+      <c r="C18">
+        <v>121354.921875</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>121040.3515625</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>121005.2734375</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>120327.75</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>119903.5625</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>119326.3203125</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>118247.6015625</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>116086.609375</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>115286.4140625</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>115165.6015625</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>115147.828125</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>115089.25</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>113649.078125</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>112298.015625</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>12103</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Río Verde</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>112182.46875</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>111026.9921875</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>110782.9140625</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>109012.71875</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>107675.9375</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>107549.4296875</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>106995.265625</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>12103</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Río Verde</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>105905.3359375</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>104879.8984375</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>104786.9375</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>104615.15625</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>103650.8203125</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>103061.671875</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>12103</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Río Verde</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>98930.7421875</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>94655.4921875</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>94472.265625</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>12103</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Río Verde</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>89031.9609375</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>88659.53125</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>12103</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Río Verde</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>76963.4453125</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>76.47058868408203</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>66.66666412353516</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>64.70587921142578</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>57.46268844604492</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>12103</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Río Verde</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>55.55555725097656</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>52.5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>12103</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Río Verde</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>48.96907043457031</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>48.71794891357422</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>48.67256546020508</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>48.22616577148438</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>47.33727645874023</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>46.11201858520508</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>45.94594573974609</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>45.79606628417969</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>45.72930526733398</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>45.22273635864258</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>44.74260711669922</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>44.73684310913086</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>44.49428176879883</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>44.44444274902344</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>43.54711151123047</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>43.52174758911133</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>43.36492919921875</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>43.35355758666992</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>42.48062133789063</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>41.92399215698242</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>41.85519027709961</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>12103</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Río Verde</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>12103</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Río Verde</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>37.75897979736328</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>12103</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Río Verde</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>37.03703689575195</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C89">
         <v>36.11111068725586</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>35.71428680419922</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>35.27735900878906</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>35.22727203369141</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>35.13513565063477</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>33.33333206176758</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>33.33333206176758</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>33.33333206176758</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>33.33333206176758</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>12103</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Río Verde</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>33.33333206176758</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>28.62232780456543</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>12103</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Río Verde</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>27.77777862548828</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>26.59053802490234</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>26.51162719726563</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>25.71428489685059</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>12103</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Río Verde</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>22.22222137451172</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>21.89349174499512</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>21.22124862670898</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>20.7317066192627</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>12103</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Río Verde</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>12103</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Río Verde</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>19.17404174804688</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>18.91891860961914</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>18.18181800842285</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>16.66666603088379</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>15.77495861053467</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>14.81481456756592</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>12103</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Río Verde</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>14.81481456756592</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>14.4728889465332</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>13.88888931274414</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>13.6363639831543</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>13.62552165985107</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>13.38083934783936</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>13.33333301544189</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>13.27201080322266</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>13.07280731201172</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>12103</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Río Verde</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>11.34020614624023</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>11.19402980804443</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>12103</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Río Verde</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>11.11111068725586</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>10.11670970916748</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>9.848484992980957</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>9.396725654602051</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>8.571428298950195</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>8.530805587768555</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>7.142857074737549</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>6.410256385803223</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>6.267806053161621</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>5.882352828979492</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>4.817947864532471</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>2.702702760696411</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>2.631578922271729</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>12103</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Río Verde</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
